--- a/assets/docs/lop4/Mi thuat - Lop 4.xlsx
+++ b/assets/docs/lop4/Mi thuat - Lop 4.xlsx
@@ -615,11 +615,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 1.1 CB2c: HS nêu được đặc điểm tạo hình của chạm khắc đình làng qua ảnh phóng to.</t>
-        </is>
-      </c>
+      <c r="H6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -709,11 +705,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 1.1 CB2c: HS nêu được cách diễn tả không gian riêng của tranh dân gian.</t>
-        </is>
-      </c>
+      <c r="H9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -739,11 +731,7 @@
           <t>7</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 1.1 CB2c: HS nêu được cách diễn tả không gian riêng của tranh dân gian.</t>
-        </is>
-      </c>
+      <c r="H10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
